--- a/templates/sample_sequence.xlsx
+++ b/templates/sample_sequence.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,7 +433,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BLK_01</v>
+        <v>CRM_HIGH</v>
       </c>
       <c r="B2" t="str">
         <v>Pb</v>
@@ -445,13 +445,13 @@
         <v>Acqua</v>
       </c>
       <c r="E2">
-        <v>0.1</v>
+        <v>84</v>
       </c>
       <c r="F2" t="str">
         <v>ug/L</v>
       </c>
       <c r="G2" t="str">
-        <v>2023-10-01T10:00:00</v>
+        <v>2023-10-01T10:05:00</v>
       </c>
       <c r="H2" t="str">
         <v>ICP01</v>
@@ -465,10 +465,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SAMP_01</v>
+        <v>SAMP_001</v>
       </c>
       <c r="B3" t="str">
-        <v>Pb</v>
+        <v>Cd</v>
       </c>
       <c r="C3" t="str">
         <v>ICP-MS</v>
@@ -477,13 +477,13 @@
         <v>Acqua</v>
       </c>
       <c r="E3">
-        <v>5.2</v>
+        <v>4.81</v>
       </c>
       <c r="F3" t="str">
         <v>ug/L</v>
       </c>
       <c r="G3" t="str">
-        <v>2023-10-01T10:05:00</v>
+        <v>2023-10-01T10:10:00</v>
       </c>
       <c r="H3" t="str">
         <v>ICP01</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CRM_LOW</v>
+        <v>SAMP_002</v>
       </c>
       <c r="B4" t="str">
         <v>Pb</v>
@@ -509,13 +509,13 @@
         <v>Acqua</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>1.23</v>
       </c>
       <c r="F4" t="str">
         <v>ug/L</v>
       </c>
       <c r="G4" t="str">
-        <v>2023-10-01T10:10:00</v>
+        <v>2023-10-01T10:15:00</v>
       </c>
       <c r="H4" t="str">
         <v>ICP01</v>
@@ -529,10 +529,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CRM_HIGH</v>
+        <v>SAMP_003</v>
       </c>
       <c r="B5" t="str">
-        <v>Pb</v>
+        <v>Cd</v>
       </c>
       <c r="C5" t="str">
         <v>ICP-MS</v>
@@ -541,13 +541,13 @@
         <v>Acqua</v>
       </c>
       <c r="E5">
-        <v>104</v>
+        <v>1.73</v>
       </c>
       <c r="F5" t="str">
         <v>ug/L</v>
       </c>
       <c r="G5" t="str">
-        <v>2023-10-01T10:15:00</v>
+        <v>2023-10-01T10:20:00</v>
       </c>
       <c r="H5" t="str">
         <v>ICP01</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SAMP_02</v>
+        <v>SAMP_004</v>
       </c>
       <c r="B6" t="str">
         <v>Pb</v>
@@ -573,13 +573,13 @@
         <v>Acqua</v>
       </c>
       <c r="E6">
-        <v>2.1</v>
+        <v>4.26</v>
       </c>
       <c r="F6" t="str">
         <v>ug/L</v>
       </c>
       <c r="G6" t="str">
-        <v>2023-10-01T10:20:00</v>
+        <v>2023-10-01T10:25:00</v>
       </c>
       <c r="H6" t="str">
         <v>ICP01</v>
@@ -593,10 +593,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DUP_01</v>
+        <v>SAMP_005</v>
       </c>
       <c r="B7" t="str">
-        <v>Pb</v>
+        <v>Cd</v>
       </c>
       <c r="C7" t="str">
         <v>ICP-MS</v>
@@ -605,13 +605,13 @@
         <v>Acqua</v>
       </c>
       <c r="E7">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="F7" t="str">
         <v>ug/L</v>
       </c>
       <c r="G7" t="str">
-        <v>2023-10-01T10:25:00</v>
+        <v>2023-10-01T10:30:00</v>
       </c>
       <c r="H7" t="str">
         <v>ICP01</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BLK_02</v>
+        <v>CRM_HIGH</v>
       </c>
       <c r="B8" t="str">
         <v>Pb</v>
@@ -637,30 +637,30 @@
         <v>Acqua</v>
       </c>
       <c r="E8">
-        <v>0.05</v>
+        <v>105.43</v>
       </c>
       <c r="F8" t="str">
         <v>ug/L</v>
       </c>
       <c r="G8" t="str">
-        <v>2023-10-02T10:00:00</v>
+        <v>2023-10-01T10:35:00</v>
       </c>
       <c r="H8" t="str">
         <v>ICP01</v>
       </c>
       <c r="I8" t="str">
-        <v>Luigi Verdi</v>
+        <v>Mario Rossi</v>
       </c>
       <c r="J8" t="str">
-        <v>B002</v>
+        <v>B001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CRM_LOW</v>
+        <v>SAMP_007</v>
       </c>
       <c r="B9" t="str">
-        <v>Pb</v>
+        <v>Cd</v>
       </c>
       <c r="C9" t="str">
         <v>ICP-MS</v>
@@ -669,27 +669,27 @@
         <v>Acqua</v>
       </c>
       <c r="E9">
-        <v>44</v>
+        <v>3.12</v>
       </c>
       <c r="F9" t="str">
         <v>ug/L</v>
       </c>
       <c r="G9" t="str">
-        <v>2023-10-02T10:05:00</v>
+        <v>2023-10-01T10:40:00</v>
       </c>
       <c r="H9" t="str">
         <v>ICP01</v>
       </c>
       <c r="I9" t="str">
-        <v>Luigi Verdi</v>
+        <v>Mario Rossi</v>
       </c>
       <c r="J9" t="str">
-        <v>B002</v>
+        <v>B001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CRM_HIGH</v>
+        <v>SAMP_008</v>
       </c>
       <c r="B10" t="str">
         <v>Pb</v>
@@ -701,27 +701,27 @@
         <v>Acqua</v>
       </c>
       <c r="E10">
-        <v>111</v>
+        <v>5.05</v>
       </c>
       <c r="F10" t="str">
         <v>ug/L</v>
       </c>
       <c r="G10" t="str">
-        <v>2023-10-02T10:10:00</v>
+        <v>2023-10-01T10:45:00</v>
       </c>
       <c r="H10" t="str">
         <v>ICP01</v>
       </c>
       <c r="I10" t="str">
-        <v>Luigi Verdi</v>
+        <v>Mario Rossi</v>
       </c>
       <c r="J10" t="str">
-        <v>B002</v>
+        <v>B001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>BLK_01</v>
+        <v>SAMP_009</v>
       </c>
       <c r="B11" t="str">
         <v>Cd</v>
@@ -733,13 +733,13 @@
         <v>Acqua</v>
       </c>
       <c r="E11">
-        <v>0.01</v>
+        <v>4.6</v>
       </c>
       <c r="F11" t="str">
         <v>ug/L</v>
       </c>
       <c r="G11" t="str">
-        <v>2023-10-01T10:00:00</v>
+        <v>2023-10-01T10:50:00</v>
       </c>
       <c r="H11" t="str">
         <v>ICP01</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CRM_STD</v>
+        <v>SAMP_010</v>
       </c>
       <c r="B12" t="str">
-        <v>Cd</v>
+        <v>Pb</v>
       </c>
       <c r="C12" t="str">
         <v>ICP-MS</v>
@@ -765,13 +765,13 @@
         <v>Acqua</v>
       </c>
       <c r="E12">
-        <v>9.8</v>
+        <v>1.48</v>
       </c>
       <c r="F12" t="str">
         <v>ug/L</v>
       </c>
       <c r="G12" t="str">
-        <v>2023-10-01T10:10:00</v>
+        <v>2023-10-01T10:55:00</v>
       </c>
       <c r="H12" t="str">
         <v>ICP01</v>
@@ -783,9 +783,3497 @@
         <v>B001</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SAMP_011</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E13">
+        <v>2.28</v>
+      </c>
+      <c r="F13" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2023-10-01T11:00:00</v>
+      </c>
+      <c r="H13" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J13" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E14">
+        <v>110.2</v>
+      </c>
+      <c r="F14" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2023-10-01T11:05:00</v>
+      </c>
+      <c r="H14" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J14" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SAMP_013</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E15">
+        <v>4.55</v>
+      </c>
+      <c r="F15" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2023-10-01T11:10:00</v>
+      </c>
+      <c r="H15" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J15" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SAMP_014</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E16">
+        <v>4.9</v>
+      </c>
+      <c r="F16" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2023-10-01T11:15:00</v>
+      </c>
+      <c r="H16" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J16" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SAMP_015</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C17" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E17">
+        <v>1.38</v>
+      </c>
+      <c r="F17" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2023-10-01T11:20:00</v>
+      </c>
+      <c r="H17" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J17" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SAMP_016</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C18" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E18">
+        <v>9.8</v>
+      </c>
+      <c r="F18" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2023-10-01T11:25:00</v>
+      </c>
+      <c r="H18" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J18" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SAMP_017</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E19">
+        <v>2.99</v>
+      </c>
+      <c r="F19" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2023-10-01T11:30:00</v>
+      </c>
+      <c r="H19" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J19" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C20" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E20">
+        <v>106.02</v>
+      </c>
+      <c r="F20" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2023-10-01T11:35:00</v>
+      </c>
+      <c r="H20" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J20" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SAMP_019</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E21">
+        <v>2.8</v>
+      </c>
+      <c r="F21" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2023-10-01T11:40:00</v>
+      </c>
+      <c r="H21" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J21" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SAMP_020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E22">
+        <v>1.99</v>
+      </c>
+      <c r="F22" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2023-10-01T11:45:00</v>
+      </c>
+      <c r="H22" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J22" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SAMP_021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E23">
+        <v>2.65</v>
+      </c>
+      <c r="F23" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2023-10-01T11:50:00</v>
+      </c>
+      <c r="H23" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J23" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SAMP_022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C24" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E24">
+        <v>4.5</v>
+      </c>
+      <c r="F24" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2023-10-01T11:55:00</v>
+      </c>
+      <c r="H24" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J24" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SAMP_023</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E25">
+        <v>1.6</v>
+      </c>
+      <c r="F25" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2023-10-01T12:00:00</v>
+      </c>
+      <c r="H25" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J25" t="str">
+        <v>B001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E26">
+        <v>93.36</v>
+      </c>
+      <c r="F26" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2023-10-01T12:05:00</v>
+      </c>
+      <c r="H26" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J26" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SAMP_025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E27">
+        <v>3.88</v>
+      </c>
+      <c r="F27" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2023-10-01T12:10:00</v>
+      </c>
+      <c r="H27" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J27" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SAMP_026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C28" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E28">
+        <v>2.8</v>
+      </c>
+      <c r="F28" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2023-10-01T12:15:00</v>
+      </c>
+      <c r="H28" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J28" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SAMP_027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E29">
+        <v>4.86</v>
+      </c>
+      <c r="F29" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2023-10-01T12:20:00</v>
+      </c>
+      <c r="H29" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J29" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SAMP_028</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E30">
+        <v>0.33</v>
+      </c>
+      <c r="F30" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2023-10-01T12:25:00</v>
+      </c>
+      <c r="H30" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J30" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SAMP_029</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E31">
+        <v>0.67</v>
+      </c>
+      <c r="F31" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2023-10-01T12:30:00</v>
+      </c>
+      <c r="H31" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J31" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E32">
+        <v>100.6</v>
+      </c>
+      <c r="F32" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2023-10-01T12:35:00</v>
+      </c>
+      <c r="H32" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J32" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SAMP_031</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E33">
+        <v>3.4</v>
+      </c>
+      <c r="F33" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2023-10-01T12:40:00</v>
+      </c>
+      <c r="H33" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J33" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SAMP_032</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E34">
+        <v>2.31</v>
+      </c>
+      <c r="F34" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2023-10-01T12:45:00</v>
+      </c>
+      <c r="H34" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J34" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SAMP_033</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C35" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E35">
+        <v>0.12</v>
+      </c>
+      <c r="F35" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G35" t="str">
+        <v>2023-10-01T12:50:00</v>
+      </c>
+      <c r="H35" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J35" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SAMP_034</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E36">
+        <v>4.06</v>
+      </c>
+      <c r="F36" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G36" t="str">
+        <v>2023-10-01T12:55:00</v>
+      </c>
+      <c r="H36" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J36" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SAMP_035</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C37" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E37">
+        <v>2.93</v>
+      </c>
+      <c r="F37" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G37" t="str">
+        <v>2023-10-01T13:00:00</v>
+      </c>
+      <c r="H37" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J37" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E38">
+        <v>99.73</v>
+      </c>
+      <c r="F38" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G38" t="str">
+        <v>2023-10-01T13:05:00</v>
+      </c>
+      <c r="H38" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J38" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SAMP_037</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E39">
+        <v>1.6</v>
+      </c>
+      <c r="F39" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G39" t="str">
+        <v>2023-10-01T13:10:00</v>
+      </c>
+      <c r="H39" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J39" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SAMP_038</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E40">
+        <v>2.5</v>
+      </c>
+      <c r="F40" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G40" t="str">
+        <v>2023-10-01T13:15:00</v>
+      </c>
+      <c r="H40" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J40" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SAMP_039</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C41" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E41">
+        <v>1.26</v>
+      </c>
+      <c r="F41" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G41" t="str">
+        <v>2023-10-01T13:20:00</v>
+      </c>
+      <c r="H41" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J41" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SAMP_040</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E42">
+        <v>2.65</v>
+      </c>
+      <c r="F42" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G42" t="str">
+        <v>2023-10-01T13:25:00</v>
+      </c>
+      <c r="H42" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J42" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SAMP_041</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E43">
+        <v>1.37</v>
+      </c>
+      <c r="F43" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G43" t="str">
+        <v>2023-10-01T13:30:00</v>
+      </c>
+      <c r="H43" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J43" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C44" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E44">
+        <v>110.23</v>
+      </c>
+      <c r="F44" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G44" t="str">
+        <v>2023-10-01T13:35:00</v>
+      </c>
+      <c r="H44" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J44" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SAMP_043</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C45" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E45">
+        <v>4.32</v>
+      </c>
+      <c r="F45" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G45" t="str">
+        <v>2023-10-01T13:40:00</v>
+      </c>
+      <c r="H45" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J45" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SAMP_044</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C46" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E46">
+        <v>3.73</v>
+      </c>
+      <c r="F46" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G46" t="str">
+        <v>2023-10-01T13:45:00</v>
+      </c>
+      <c r="H46" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J46" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SAMP_045</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C47" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E47">
+        <v>2.66</v>
+      </c>
+      <c r="F47" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G47" t="str">
+        <v>2023-10-01T13:50:00</v>
+      </c>
+      <c r="H47" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J47" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SAMP_046</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C48" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E48">
+        <v>7.36</v>
+      </c>
+      <c r="F48" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G48" t="str">
+        <v>2023-10-01T13:55:00</v>
+      </c>
+      <c r="H48" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J48" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SAMP_047</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C49" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E49">
+        <v>4.26</v>
+      </c>
+      <c r="F49" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G49" t="str">
+        <v>2023-10-01T14:00:00</v>
+      </c>
+      <c r="H49" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J49" t="str">
+        <v>B002</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C50" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E50">
+        <v>99.32</v>
+      </c>
+      <c r="F50" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G50" t="str">
+        <v>2023-10-01T14:05:00</v>
+      </c>
+      <c r="H50" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J50" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SAMP_049</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C51" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E51">
+        <v>0.79</v>
+      </c>
+      <c r="F51" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G51" t="str">
+        <v>2023-10-01T14:10:00</v>
+      </c>
+      <c r="H51" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J51" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>SAMP_050</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C52" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E52">
+        <v>2.35</v>
+      </c>
+      <c r="F52" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G52" t="str">
+        <v>2023-10-01T14:15:00</v>
+      </c>
+      <c r="H52" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J52" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SAMP_051</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C53" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E53">
+        <v>1.83</v>
+      </c>
+      <c r="F53" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G53" t="str">
+        <v>2023-10-01T14:20:00</v>
+      </c>
+      <c r="H53" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J53" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SAMP_052</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C54" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E54">
+        <v>3.52</v>
+      </c>
+      <c r="F54" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G54" t="str">
+        <v>2023-10-01T14:25:00</v>
+      </c>
+      <c r="H54" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J54" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SAMP_053</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C55" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E55">
+        <v>2.36</v>
+      </c>
+      <c r="F55" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G55" t="str">
+        <v>2023-10-01T14:30:00</v>
+      </c>
+      <c r="H55" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J55" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C56" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E56">
+        <v>102.93</v>
+      </c>
+      <c r="F56" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G56" t="str">
+        <v>2023-10-01T14:35:00</v>
+      </c>
+      <c r="H56" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J56" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>SAMP_055</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C57" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E57">
+        <v>3.94</v>
+      </c>
+      <c r="F57" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G57" t="str">
+        <v>2023-10-01T14:40:00</v>
+      </c>
+      <c r="H57" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J57" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>SAMP_056</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C58" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E58">
+        <v>6.08</v>
+      </c>
+      <c r="F58" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G58" t="str">
+        <v>2023-10-01T14:45:00</v>
+      </c>
+      <c r="H58" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J58" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SAMP_057</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C59" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E59">
+        <v>1.25</v>
+      </c>
+      <c r="F59" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G59" t="str">
+        <v>2023-10-01T14:50:00</v>
+      </c>
+      <c r="H59" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J59" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SAMP_058</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C60" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E60">
+        <v>3.29</v>
+      </c>
+      <c r="F60" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G60" t="str">
+        <v>2023-10-01T14:55:00</v>
+      </c>
+      <c r="H60" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J60" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>SAMP_059</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C61" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E61">
+        <v>3.24</v>
+      </c>
+      <c r="F61" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G61" t="str">
+        <v>2023-10-01T15:00:00</v>
+      </c>
+      <c r="H61" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J61" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C62" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E62">
+        <v>101.77</v>
+      </c>
+      <c r="F62" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G62" t="str">
+        <v>2023-10-01T15:05:00</v>
+      </c>
+      <c r="H62" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J62" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>SAMP_061</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C63" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E63">
+        <v>1.16</v>
+      </c>
+      <c r="F63" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G63" t="str">
+        <v>2023-10-01T15:10:00</v>
+      </c>
+      <c r="H63" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J63" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>SAMP_062</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C64" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E64">
+        <v>2.03</v>
+      </c>
+      <c r="F64" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G64" t="str">
+        <v>2023-10-01T15:15:00</v>
+      </c>
+      <c r="H64" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J64" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SAMP_063</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C65" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E65">
+        <v>0.92</v>
+      </c>
+      <c r="F65" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G65" t="str">
+        <v>2023-10-01T15:20:00</v>
+      </c>
+      <c r="H65" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J65" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SAMP_064</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C66" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E66">
+        <v>6.71</v>
+      </c>
+      <c r="F66" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G66" t="str">
+        <v>2023-10-01T15:25:00</v>
+      </c>
+      <c r="H66" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J66" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SAMP_065</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C67" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E67">
+        <v>4.52</v>
+      </c>
+      <c r="F67" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G67" t="str">
+        <v>2023-10-01T15:30:00</v>
+      </c>
+      <c r="H67" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J67" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C68" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E68">
+        <v>95.36</v>
+      </c>
+      <c r="F68" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G68" t="str">
+        <v>2023-10-01T15:35:00</v>
+      </c>
+      <c r="H68" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J68" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SAMP_067</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C69" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E69">
+        <v>2.07</v>
+      </c>
+      <c r="F69" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G69" t="str">
+        <v>2023-10-01T15:40:00</v>
+      </c>
+      <c r="H69" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J69" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SAMP_068</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C70" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E70">
+        <v>5.79</v>
+      </c>
+      <c r="F70" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G70" t="str">
+        <v>2023-10-01T15:45:00</v>
+      </c>
+      <c r="H70" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J70" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SAMP_069</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C71" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E71">
+        <v>4.55</v>
+      </c>
+      <c r="F71" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G71" t="str">
+        <v>2023-10-01T15:50:00</v>
+      </c>
+      <c r="H71" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J71" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SAMP_070</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C72" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E72">
+        <v>8.71</v>
+      </c>
+      <c r="F72" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G72" t="str">
+        <v>2023-10-01T15:55:00</v>
+      </c>
+      <c r="H72" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J72" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>SAMP_071</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C73" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E73">
+        <v>1.78</v>
+      </c>
+      <c r="F73" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G73" t="str">
+        <v>2023-10-01T16:00:00</v>
+      </c>
+      <c r="H73" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J73" t="str">
+        <v>B003</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C74" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E74">
+        <v>104.11</v>
+      </c>
+      <c r="F74" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G74" t="str">
+        <v>2023-10-01T16:05:00</v>
+      </c>
+      <c r="H74" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J74" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>SAMP_073</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C75" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E75">
+        <v>1.25</v>
+      </c>
+      <c r="F75" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G75" t="str">
+        <v>2023-10-01T16:10:00</v>
+      </c>
+      <c r="H75" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J75" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>SAMP_074</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C76" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E76">
+        <v>4.93</v>
+      </c>
+      <c r="F76" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G76" t="str">
+        <v>2023-10-01T16:15:00</v>
+      </c>
+      <c r="H76" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J76" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SAMP_075</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C77" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E77">
+        <v>0.16</v>
+      </c>
+      <c r="F77" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G77" t="str">
+        <v>2023-10-01T16:20:00</v>
+      </c>
+      <c r="H77" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J77" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SAMP_076</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C78" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E78">
+        <v>4.98</v>
+      </c>
+      <c r="F78" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G78" t="str">
+        <v>2023-10-01T16:25:00</v>
+      </c>
+      <c r="H78" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J78" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SAMP_077</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C79" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E79">
+        <v>2.09</v>
+      </c>
+      <c r="F79" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G79" t="str">
+        <v>2023-10-01T16:30:00</v>
+      </c>
+      <c r="H79" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J79" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C80" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E80">
+        <v>101.29</v>
+      </c>
+      <c r="F80" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G80" t="str">
+        <v>2023-10-01T16:35:00</v>
+      </c>
+      <c r="H80" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J80" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>SAMP_079</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C81" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E81">
+        <v>3.82</v>
+      </c>
+      <c r="F81" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G81" t="str">
+        <v>2023-10-01T16:40:00</v>
+      </c>
+      <c r="H81" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J81" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>SAMP_080</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C82" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E82">
+        <v>9.62</v>
+      </c>
+      <c r="F82" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G82" t="str">
+        <v>2023-10-01T16:45:00</v>
+      </c>
+      <c r="H82" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J82" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>SAMP_081</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C83" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E83">
+        <v>1.71</v>
+      </c>
+      <c r="F83" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G83" t="str">
+        <v>2023-10-01T16:50:00</v>
+      </c>
+      <c r="H83" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J83" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>SAMP_082</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C84" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E84">
+        <v>6.43</v>
+      </c>
+      <c r="F84" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G84" t="str">
+        <v>2023-10-01T16:55:00</v>
+      </c>
+      <c r="H84" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J84" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>SAMP_083</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C85" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E85">
+        <v>1.96</v>
+      </c>
+      <c r="F85" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G85" t="str">
+        <v>2023-10-01T17:00:00</v>
+      </c>
+      <c r="H85" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J85" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C86" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E86">
+        <v>99.55</v>
+      </c>
+      <c r="F86" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G86" t="str">
+        <v>2023-10-01T17:05:00</v>
+      </c>
+      <c r="H86" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J86" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>SAMP_085</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C87" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E87">
+        <v>1.44</v>
+      </c>
+      <c r="F87" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G87" t="str">
+        <v>2023-10-01T17:10:00</v>
+      </c>
+      <c r="H87" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J87" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>SAMP_086</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C88" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E88">
+        <v>3.57</v>
+      </c>
+      <c r="F88" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G88" t="str">
+        <v>2023-10-01T17:15:00</v>
+      </c>
+      <c r="H88" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J88" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>SAMP_087</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C89" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E89">
+        <v>3.43</v>
+      </c>
+      <c r="F89" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G89" t="str">
+        <v>2023-10-01T17:20:00</v>
+      </c>
+      <c r="H89" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J89" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>SAMP_088</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C90" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E90">
+        <v>7.74</v>
+      </c>
+      <c r="F90" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2023-10-01T17:25:00</v>
+      </c>
+      <c r="H90" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J90" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>SAMP_089</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C91" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E91">
+        <v>0.5</v>
+      </c>
+      <c r="F91" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G91" t="str">
+        <v>2023-10-01T17:30:00</v>
+      </c>
+      <c r="H91" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J91" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C92" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E92">
+        <v>95.75</v>
+      </c>
+      <c r="F92" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G92" t="str">
+        <v>2023-10-01T17:35:00</v>
+      </c>
+      <c r="H92" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J92" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>SAMP_091</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C93" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E93">
+        <v>3.18</v>
+      </c>
+      <c r="F93" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2023-10-01T17:40:00</v>
+      </c>
+      <c r="H93" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J93" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>SAMP_092</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C94" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E94">
+        <v>4.67</v>
+      </c>
+      <c r="F94" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2023-10-01T17:45:00</v>
+      </c>
+      <c r="H94" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J94" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>SAMP_093</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C95" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E95">
+        <v>1.3</v>
+      </c>
+      <c r="F95" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G95" t="str">
+        <v>2023-10-01T17:50:00</v>
+      </c>
+      <c r="H95" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J95" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>SAMP_094</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C96" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E96">
+        <v>1.24</v>
+      </c>
+      <c r="F96" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G96" t="str">
+        <v>2023-10-01T17:55:00</v>
+      </c>
+      <c r="H96" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J96" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>SAMP_095</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C97" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E97">
+        <v>3.01</v>
+      </c>
+      <c r="F97" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G97" t="str">
+        <v>2023-10-01T18:00:00</v>
+      </c>
+      <c r="H97" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J97" t="str">
+        <v>B004</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C98" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E98">
+        <v>89.28</v>
+      </c>
+      <c r="F98" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2023-10-01T18:05:00</v>
+      </c>
+      <c r="H98" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J98" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>SAMP_097</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C99" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E99">
+        <v>1.24</v>
+      </c>
+      <c r="F99" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G99" t="str">
+        <v>2023-10-01T18:10:00</v>
+      </c>
+      <c r="H99" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J99" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>SAMP_098</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C100" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E100">
+        <v>8.48</v>
+      </c>
+      <c r="F100" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2023-10-01T18:15:00</v>
+      </c>
+      <c r="H100" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J100" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>SAMP_099</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C101" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E101">
+        <v>1.92</v>
+      </c>
+      <c r="F101" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2023-10-01T18:20:00</v>
+      </c>
+      <c r="H101" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J101" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>SAMP_100</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E102">
+        <v>9.69</v>
+      </c>
+      <c r="F102" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G102" t="str">
+        <v>2023-10-01T18:25:00</v>
+      </c>
+      <c r="H102" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J102" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>SAMP_101</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E103">
+        <v>4.01</v>
+      </c>
+      <c r="F103" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2023-10-01T18:30:00</v>
+      </c>
+      <c r="H103" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J103" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E104">
+        <v>107.16</v>
+      </c>
+      <c r="F104" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G104" t="str">
+        <v>2023-10-01T18:35:00</v>
+      </c>
+      <c r="H104" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J104" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>SAMP_103</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C105" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E105">
+        <v>2.74</v>
+      </c>
+      <c r="F105" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G105" t="str">
+        <v>2023-10-01T18:40:00</v>
+      </c>
+      <c r="H105" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J105" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>SAMP_104</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C106" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E106">
+        <v>3.35</v>
+      </c>
+      <c r="F106" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G106" t="str">
+        <v>2023-10-01T18:45:00</v>
+      </c>
+      <c r="H106" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J106" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>SAMP_105</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C107" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E107">
+        <v>1.13</v>
+      </c>
+      <c r="F107" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G107" t="str">
+        <v>2023-10-01T18:50:00</v>
+      </c>
+      <c r="H107" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J107" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>SAMP_106</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C108" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E108">
+        <v>6.41</v>
+      </c>
+      <c r="F108" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G108" t="str">
+        <v>2023-10-01T18:55:00</v>
+      </c>
+      <c r="H108" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J108" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>SAMP_107</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C109" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E109">
+        <v>0.55</v>
+      </c>
+      <c r="F109" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G109" t="str">
+        <v>2023-10-01T19:00:00</v>
+      </c>
+      <c r="H109" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J109" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C110" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E110">
+        <v>104.01</v>
+      </c>
+      <c r="F110" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2023-10-01T19:05:00</v>
+      </c>
+      <c r="H110" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J110" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>SAMP_109</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C111" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E111">
+        <v>1.81</v>
+      </c>
+      <c r="F111" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G111" t="str">
+        <v>2023-10-01T19:10:00</v>
+      </c>
+      <c r="H111" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J111" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>SAMP_110</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C112" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E112">
+        <v>4.89</v>
+      </c>
+      <c r="F112" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G112" t="str">
+        <v>2023-10-01T19:15:00</v>
+      </c>
+      <c r="H112" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J112" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>SAMP_111</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C113" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E113">
+        <v>2.39</v>
+      </c>
+      <c r="F113" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G113" t="str">
+        <v>2023-10-01T19:20:00</v>
+      </c>
+      <c r="H113" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I113" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J113" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>SAMP_112</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C114" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E114">
+        <v>1.74</v>
+      </c>
+      <c r="F114" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G114" t="str">
+        <v>2023-10-01T19:25:00</v>
+      </c>
+      <c r="H114" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J114" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>SAMP_113</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C115" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E115">
+        <v>2.7</v>
+      </c>
+      <c r="F115" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G115" t="str">
+        <v>2023-10-01T19:30:00</v>
+      </c>
+      <c r="H115" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J115" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>CRM_HIGH</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C116" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E116">
+        <v>106.44</v>
+      </c>
+      <c r="F116" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G116" t="str">
+        <v>2023-10-01T19:35:00</v>
+      </c>
+      <c r="H116" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I116" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J116" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>SAMP_115</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C117" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E117">
+        <v>1.47</v>
+      </c>
+      <c r="F117" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G117" t="str">
+        <v>2023-10-01T19:40:00</v>
+      </c>
+      <c r="H117" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J117" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>SAMP_116</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C118" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E118">
+        <v>9.61</v>
+      </c>
+      <c r="F118" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G118" t="str">
+        <v>2023-10-01T19:45:00</v>
+      </c>
+      <c r="H118" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J118" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>SAMP_117</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C119" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E119">
+        <v>0.99</v>
+      </c>
+      <c r="F119" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G119" t="str">
+        <v>2023-10-01T19:50:00</v>
+      </c>
+      <c r="H119" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J119" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>SAMP_118</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Pb</v>
+      </c>
+      <c r="C120" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E120">
+        <v>4.85</v>
+      </c>
+      <c r="F120" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G120" t="str">
+        <v>2023-10-01T19:55:00</v>
+      </c>
+      <c r="H120" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J120" t="str">
+        <v>B005</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>SAMP_119</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Cd</v>
+      </c>
+      <c r="C121" t="str">
+        <v>ICP-MS</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Acqua</v>
+      </c>
+      <c r="E121">
+        <v>2.62</v>
+      </c>
+      <c r="F121" t="str">
+        <v>ug/L</v>
+      </c>
+      <c r="G121" t="str">
+        <v>2023-10-01T20:00:00</v>
+      </c>
+      <c r="H121" t="str">
+        <v>ICP01</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Mario Rossi</v>
+      </c>
+      <c r="J121" t="str">
+        <v>B005</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J121"/>
   </ignoredErrors>
 </worksheet>
 </file>